--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6037,7 +6037,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>175</v>
       </c>
@@ -6056,7 +6056,7 @@
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -6342,7 +6342,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>183</v>
       </c>
@@ -6357,13 +6357,13 @@
         <v>62</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -6445,7 +6445,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>187</v>
       </c>
@@ -6460,13 +6460,13 @@
         <v>188</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -6754,7 +6754,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>201</v>
       </c>
@@ -6775,7 +6775,7 @@
         <v>75</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-item-plan-traitement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
